--- a/isms-core-framework/A.5-organisational-controls/isms-a.5.31-legal-statutory-regulatory-contractual-requirements/WKBK/ISMS-IMP-A.5.31.5_Evidence_Register_20260301.xlsx
+++ b/isms-core-framework/A.5-organisational-controls/isms-a.5.31-legal-statutory-regulatory-contractual-requirements/WKBK/ISMS-IMP-A.5.31.5_Evidence_Register_20260301.xlsx
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="H5" s="16" t="n">
-        <v>46022.50845255941</v>
+        <v>46022.74822729941</v>
       </c>
       <c r="I5" s="16" t="n">
-        <v>46447.50845255941</v>
+        <v>46447.74822729941</v>
       </c>
       <c r="J5" s="14" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         </is>
       </c>
       <c r="N5" s="16" t="n">
-        <v>46447.50845255941</v>
+        <v>46447.74822729941</v>
       </c>
       <c r="O5" s="15" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         </is>
       </c>
       <c r="Q5" s="16" t="n">
-        <v>46082.50845255941</v>
+        <v>46082.74822729941</v>
       </c>
     </row>
     <row r="6">
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="H6" s="16" t="n">
-        <v>46037.50845255941</v>
+        <v>46037.74822729941</v>
       </c>
       <c r="I6" s="16" t="n">
-        <v>46447.50845255941</v>
+        <v>46447.74822729941</v>
       </c>
       <c r="J6" s="14" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="N6" s="16" t="n">
-        <v>46447.50845255941</v>
+        <v>46447.74822729941</v>
       </c>
       <c r="O6" s="15" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="Q6" s="16" t="n">
-        <v>46082.50845255941</v>
+        <v>46082.74822729941</v>
       </c>
     </row>
     <row r="7">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="H7" s="16" t="n">
-        <v>45992.50845255941</v>
+        <v>45992.74822729941</v>
       </c>
       <c r="I7" s="16" t="n">
-        <v>46447.50845255941</v>
+        <v>46447.74822729941</v>
       </c>
       <c r="J7" s="14" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="N7" s="16" t="n">
-        <v>46447.50845255941</v>
+        <v>46447.74822729941</v>
       </c>
       <c r="O7" s="15" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         </is>
       </c>
       <c r="Q7" s="16" t="n">
-        <v>46082.50845255941</v>
+        <v>46082.74822729941</v>
       </c>
     </row>
     <row r="8">
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="H8" s="16" t="n">
-        <v>45902.50845255941</v>
+        <v>45902.74822729941</v>
       </c>
       <c r="I8" s="14" t="n"/>
       <c r="J8" s="14" t="inlineStr">
@@ -1464,7 +1464,7 @@
         </is>
       </c>
       <c r="Q8" s="16" t="n">
-        <v>46082.50845255941</v>
+        <v>46082.74822729941</v>
       </c>
     </row>
     <row r="9">
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="H9" s="16" t="n">
-        <v>46052.50845255941</v>
+        <v>46052.74822729941</v>
       </c>
       <c r="I9" s="16" t="n">
-        <v>46417.50845255941</v>
+        <v>46417.74822729941</v>
       </c>
       <c r="J9" s="14" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="N9" s="16" t="n">
-        <v>46417.50845255941</v>
+        <v>46417.74822729941</v>
       </c>
       <c r="O9" s="15" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         </is>
       </c>
       <c r="Q9" s="16" t="n">
-        <v>46082.50845255941</v>
+        <v>46082.74822729941</v>
       </c>
     </row>
     <row r="10">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="H10" s="16" t="n">
-        <v>46067.50845255941</v>
+        <v>46067.74822729941</v>
       </c>
       <c r="I10" s="16" t="n">
-        <v>46432.50845255941</v>
+        <v>46432.74822729941</v>
       </c>
       <c r="J10" s="14" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         </is>
       </c>
       <c r="N10" s="16" t="n">
-        <v>46432.50845255941</v>
+        <v>46432.74822729941</v>
       </c>
       <c r="O10" s="15" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         </is>
       </c>
       <c r="Q10" s="16" t="n">
-        <v>46082.50845255941</v>
+        <v>46082.74822729941</v>
       </c>
     </row>
     <row r="11">
@@ -1662,7 +1662,7 @@
         </is>
       </c>
       <c r="H11" s="16" t="n">
-        <v>46077.50845255941</v>
+        <v>46077.74822729941</v>
       </c>
       <c r="I11" s="14" t="n"/>
       <c r="J11" s="14" t="inlineStr">
@@ -1686,7 +1686,7 @@
         </is>
       </c>
       <c r="N11" s="16" t="n">
-        <v>46102.50845255941</v>
+        <v>46102.74822729941</v>
       </c>
       <c r="O11" s="15" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="Q11" s="16" t="n">
-        <v>46082.50845255941</v>
+        <v>46082.74822729941</v>
       </c>
     </row>
     <row r="12">
@@ -1772,7 +1772,7 @@
         </is>
       </c>
       <c r="Q12" s="16" t="n">
-        <v>46082.50845255941</v>
+        <v>46082.74822729941</v>
       </c>
     </row>
     <row r="13">
@@ -1812,10 +1812,10 @@
         </is>
       </c>
       <c r="H13" s="16" t="n">
-        <v>46072.50845255941</v>
+        <v>46072.74822729941</v>
       </c>
       <c r="I13" s="16" t="n">
-        <v>46162.50845255941</v>
+        <v>46162.74822729941</v>
       </c>
       <c r="J13" s="14" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         </is>
       </c>
       <c r="N13" s="16" t="n">
-        <v>46102.50845255941</v>
+        <v>46102.74822729941</v>
       </c>
       <c r="O13" s="15" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         </is>
       </c>
       <c r="Q13" s="16" t="n">
-        <v>46082.50845255941</v>
+        <v>46082.74822729941</v>
       </c>
     </row>
     <row r="14">
@@ -1891,10 +1891,10 @@
         </is>
       </c>
       <c r="H14" s="16" t="n">
-        <v>46080.50845255941</v>
+        <v>46080.74822729941</v>
       </c>
       <c r="I14" s="16" t="n">
-        <v>46110.50845255941</v>
+        <v>46110.74822729941</v>
       </c>
       <c r="J14" s="14" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="N14" s="16" t="n">
-        <v>46110.50845255941</v>
+        <v>46110.74822729941</v>
       </c>
       <c r="O14" s="15" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="Q14" s="16" t="n">
-        <v>46082.50845255941</v>
+        <v>46082.74822729941</v>
       </c>
     </row>
     <row r="15">
@@ -1970,10 +1970,10 @@
         </is>
       </c>
       <c r="H15" s="16" t="n">
-        <v>45992.50845255941</v>
+        <v>45992.74822729941</v>
       </c>
       <c r="I15" s="16" t="n">
-        <v>46052.50845255941</v>
+        <v>46052.74822729941</v>
       </c>
       <c r="J15" s="14" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         </is>
       </c>
       <c r="N15" s="16" t="n">
-        <v>46052.50845255941</v>
+        <v>46052.74822729941</v>
       </c>
       <c r="O15" s="15" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="Q15" s="16" t="n">
-        <v>46082.50845255941</v>
+        <v>46082.74822729941</v>
       </c>
     </row>
     <row r="16">
